--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_ADO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_ADO.xlsx
@@ -21,14 +21,14 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,42 +590,42 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>143</v>
+      </c>
+      <c r="D2" t="n">
+        <v>64</v>
+      </c>
+      <c r="E2" t="n">
+        <v>157</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>44.8%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>72</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>48.6%</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>71</v>
       </c>
-      <c r="D2" t="n">
-        <v>33</v>
-      </c>
-      <c r="E2" t="n">
-        <v>83</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>46.5%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>32</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>39</v>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,27 +646,27 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -681,11 +681,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -767,40 +767,130 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ADO_L._AYERS</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>L. Ayers</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>18</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>34.4%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ADO_D._CAMBRIDGE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D. Cambridge</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>13</v>
+      </c>
+      <c r="E4" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>61.9%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K2"/>
+  <autoFilter ref="A1:K4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -815,7 +905,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="43" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -838,7 +928,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: L. Ayers (16 L)</t>
+          <t>Maior volume: L. Ayers (32 L)</t>
         </is>
       </c>
     </row>
@@ -850,7 +940,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: L. Ayers (9 3PA)</t>
+          <t>Maior volume 3pt: L. Ayers (14 3PA)</t>
         </is>
       </c>
     </row>
@@ -874,7 +964,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (31 L)</t>
+          <t>Zona mais usada: Above the Break 3 (48 L)</t>
         </is>
       </c>
     </row>
@@ -886,7 +976,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Above the Break 3 (54.8%)</t>
+          <t>Zona mais eficaz: Restricted Area (53.3%)</t>
         </is>
       </c>
     </row>
@@ -902,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1035,13 +1125,13 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>32</v>
+      </c>
+      <c r="D2" t="n">
         <v>16</v>
       </c>
-      <c r="D2" t="n">
-        <v>8</v>
-      </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1049,16 +1139,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1070,24 +1160,24 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>8</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1112,116 +1202,120 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>13</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>35.7%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>3</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>66.7%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADO_J._PALM</t>
+          <t>ADO_J._WOOD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Palm</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
+        <v>7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
         <v>4</v>
       </c>
-      <c r="E4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>6</v>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>50.0%</t>
@@ -1229,7 +1323,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -1244,52 +1338,52 @@
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>7</v>
       </c>
-      <c r="D5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>14</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1301,16 +1395,16 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -1321,69 +1415,69 @@
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADO_J._WOOD</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="C6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D6" t="n">
         <v>6</v>
       </c>
-      <c r="D6" t="n">
-        <v>3</v>
-      </c>
       <c r="E6" t="n">
+        <v>16</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>9</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>64.3%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>7</v>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>2</v>
-      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -1391,17 +1485,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -1416,200 +1510,192 @@
         </is>
       </c>
       <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>6</v>
       </c>
-      <c r="D7" t="n">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="n">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
         <v>6</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="R7" t="n">
         <v>5</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>83.3%</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>4</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7</v>
-      </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADO_M._MONTEIRO</t>
+          <t>ADO_J._PALM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>J. Palm</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
         <v>6</v>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>4</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADO_N._MORAIS</t>
+          <t>ADO_J._SILVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>N. Morais</t>
+          <t>J. Silva</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1622,40 +1708,40 @@
         <v>3</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADO_T._PINTO</t>
+          <t>ADO_N._MORAIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T. Pinto</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1664,7 +1750,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1672,34 +1758,24 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1714,63 +1790,217 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
+        <v>12</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
         <v>3</v>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>1</v>
-      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
       <c r="Q11" t="n">
         <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ADO_T._PINTO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>T. Pinto</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>11</v>
+      </c>
+      <c r="R12" t="n">
+        <v>12</v>
+      </c>
+      <c r="S12" t="n">
         <v>9</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ADO_R._SONA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>R. Sona</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="n">
+        <v>12</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S11"/>
+  <autoFilter ref="A1:S13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1781,7 +2011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1922,51 +2152,51 @@
         </is>
       </c>
       <c r="E2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F2" t="n">
         <v>16</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
+        <v>39</v>
+      </c>
+      <c r="H2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>11</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>8</v>
       </c>
-      <c r="G2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>56.2%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>8</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>3</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -1982,12 +2212,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADO_D._CAMBRIDGE</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D. Cambridge</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -1995,34 +2225,34 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G3" t="n">
         <v>16</v>
       </c>
       <c r="H3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -2035,29 +2265,337 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ADO_J._WOOD</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>J. Wood</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G4" t="n">
+        <v>18</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>4</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>3</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3</v>
+      </c>
+      <c r="S4" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ADO_D._CAMBRIDGE</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>D. Cambridge</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>21</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>13</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>4</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ADO_L._BOYLE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L. Boyle</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ADO_M._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>M. Monteiro</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>15</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>14.3%</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S3"/>
+  <autoFilter ref="A1:S7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2068,7 +2606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2171,26 +2709,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="I2" t="n">
         <v>1.2</v>
@@ -2201,11 +2739,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -2218,38 +2756,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_J._WOOD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -2257,45 +2795,45 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M3" t="n">
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADO_D._CAMBRIDGE</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D. Cambridge</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2309,7 +2847,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -2321,7 +2859,7 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>2</v>
@@ -2339,48 +2877,48 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>12</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>6</v>
       </c>
-      <c r="H5" t="n">
-        <v>6</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>3</v>
+      </c>
+      <c r="N5" t="n">
         <v>4</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>2</v>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -2395,14 +2933,14 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2411,13 +2949,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2425,55 +2963,55 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>5</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADO_J._WOOD</t>
+          <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -2481,55 +3019,55 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>5</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADO_M._MONTEIRO</t>
+          <t>ADO_R._SOEIRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>R. Soeiro</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D8" t="n">
         <v>4</v>
       </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>6</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -2541,107 +3079,107 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="M8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADO_T._PINTO</t>
+          <t>ADO_D._CAMBRIDGE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>T. Pinto</t>
+          <t>D. Cambridge</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
         <v>2</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="M9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADO_R._SOEIRO</t>
+          <t>ADO_T._PINTO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R. Soeiro</t>
+          <t>T. Pinto</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -2653,68 +3191,174 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="M10" t="n">
         <v>9</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ADO_J._PALM</t>
+          <t>ADO_R._SONA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Palm</t>
+          <t>R. Sona</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="M11" t="n">
         <v>10</v>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ADO_J._PALM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>J. Palm</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ADO_J._SILVA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>J. Silva</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>7</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>11</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N11"/>
+  <autoFilter ref="A1:N13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2725,28 +3369,211 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>player_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>fg3a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>fg3m</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fg3_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>three_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>shot_attempts</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>points_from_shots</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>pts_per_shot</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>top_zone_1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>top_zone_1_att</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>top_zone_1_pct</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_volume</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>team_rank_3pt_pct</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>ADO_L._AYERS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>L. Ayers</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>11</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ADO_J._WOOD</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J. Wood</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="n">
+        <v>18</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:N3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2825,32 +3652,32 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2860,17 +3687,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -2878,14 +3705,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2895,32 +3722,32 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -2930,25 +3757,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -2961,71 +3788,71 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3040,7 +3867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3051,7 +3878,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
@@ -3160,53 +3987,53 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>8</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>32</v>
+      </c>
+      <c r="M2" t="inlineStr">
         <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>2</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>16</v>
-      </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="n">
+        <v>14</v>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>9</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>44.4%</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3230,11 +4057,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3243,11 +4070,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -3264,43 +4091,43 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADO_J._PALM</t>
+          <t>ADO_J._WOOD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Palm</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -3309,7 +4136,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -3320,34 +4147,48 @@
           <t>33.3%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
       <c r="P4" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3360,54 +4201,64 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>2</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
       <c r="L5" t="n">
+        <v>15</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>7</v>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>5</v>
-      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADO_J._WOOD</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3416,16 +4267,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3433,40 +4284,40 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Mid-Range</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="7">
@@ -3486,41 +4337,41 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -3528,109 +4379,95 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADO_M._MONTEIRO</t>
+          <t>ADO_J._PALM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>J. Palm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>4</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADO_N._MORAIS</t>
+          <t>ADO_J._SILVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>N. Morais</t>
+          <t>J. Silva</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -3640,34 +4477,30 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADO_T._PINTO</t>
+          <t>ADO_N._MORAIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>T. Pinto</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3676,47 +4509,37 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11">
@@ -3736,41 +4559,171 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>6</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ADO_T._PINTO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>T. Pinto</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>2</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ADO_R._SONA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>R. Sona</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O11" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="P11" t="n">
+      <c r="N13" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P11"/>
+  <autoFilter ref="A1:P13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3781,7 +4734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3857,39 +4810,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADO_L._AYERS</t>
+          <t>ADO_D._CAMBRIDGE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>L. Ayers</t>
+          <t>D. Cambridge</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -3902,57 +4855,57 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADO_D._CAMBRIDGE</t>
+          <t>ADO_L._AYERS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D. Cambridge</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADO_J._PALM</t>
+          <t>ADO_L._AYERS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Palm</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3961,29 +4914,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -3992,50 +4945,320 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>ADO_J._SILVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Silva</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>ADO_R._WOODS</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>R. Woods</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="n">
+        <v>12</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ADO_N._MORAIS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>N. Morais</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>9</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ADO_J._PALM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>J. Palm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADO_L._BOYLE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>L. Boyle</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>6</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ADO_L._AYERS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>L. Ayers</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ADO_M._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>M. Monteiro</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="n">
-        <v>12</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K5"/>
+  <autoFilter ref="A1:K11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_ADO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_ADO.xlsx
@@ -22,13 +22,13 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$W$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'alerts'!$A$1:$B$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,54 +590,54 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>143</v>
+        <v>219</v>
       </c>
       <c r="D2" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="E2" t="n">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="I2" t="n">
+        <v>96</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>35.4%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
         <v>71</v>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>40.8%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>49.7%</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>48</v>
-      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,27 +646,27 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U2" t="n">
+        <v>5</v>
+      </c>
+      <c r="V2" t="n">
         <v>2</v>
       </c>
-      <c r="T2" t="n">
-        <v>6</v>
-      </c>
-      <c r="U2" t="n">
+      <c r="W2" t="n">
         <v>4</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W2" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -757,12 +757,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADO_L._AYERS</t>
+          <t>ADO_J._PALM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>L. Ayers</t>
+          <t>J. Palm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -771,29 +771,29 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
       <c r="F2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -812,36 +812,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -861,17 +861,17 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -879,7 +879,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -889,8 +889,368 @@
         <v>1</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ADO_J._SILVA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J. Silva</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>76.5%</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ADO_L._AYERS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L. Ayers</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" t="n">
+        <v>7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>21</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>31.1%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ADO_R._WOODS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>R. Woods</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9</v>
+      </c>
+      <c r="E7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>12</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ADO_D._CAMBRIDGE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>D. Cambridge</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADO_N._MORAIS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N. Morais</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>78.6%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ADO_M._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M. Monteiro</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>8</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>32.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ADO_L._BOYLE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>L. Boyle</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ADO_L._AYERS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>L. Ayers</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>24.4%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K4"/>
+  <autoFilter ref="A1:K12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -928,7 +1288,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: L. Ayers (32 L)</t>
+          <t>Maior volume: L. Ayers (45 L)</t>
         </is>
       </c>
     </row>
@@ -940,7 +1300,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: L. Ayers (14 3PA)</t>
+          <t>Maior volume 3pt: L. Ayers (17 3PA)</t>
         </is>
       </c>
     </row>
@@ -952,7 +1312,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: L. Ayers (1.2 pts/shot)</t>
+          <t>Mais eficaz: R. Soeiro (1.3 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -964,7 +1324,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (48 L)</t>
+          <t>Zona mais usada: Above the Break 3 (71 L)</t>
         </is>
       </c>
     </row>
@@ -976,7 +1336,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (53.3%)</t>
+          <t>Zona mais eficaz: Restricted Area (54.4%)</t>
         </is>
       </c>
     </row>
@@ -1125,66 +1485,66 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>37.8%</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>14</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>14</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>43.8%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>11</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>54.5%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>8</v>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1202,32 +1562,32 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>46.7%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>10</v>
       </c>
-      <c r="E3" t="n">
-        <v>22</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>47.6%</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
@@ -1237,11 +1597,11 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1250,46 +1610,46 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADO_J._WOOD</t>
+          <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>18</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1297,16 +1657,16 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
       <c r="J4" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -1314,76 +1674,76 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADO_M._MONTEIRO</t>
+          <t>ADO_J._WOOD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1391,16 +1751,16 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -1415,10 +1775,10 @@
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -1433,55 +1793,55 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>9</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>44.4%</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>64.3%</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>7</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>57.1%</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1492,48 +1852,44 @@
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADO_L._BOYLE</t>
+          <t>ADO_J._SILVA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>J. Silva</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -1541,38 +1897,38 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>2</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1587,17 +1943,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1610,7 +1966,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1618,11 +1974,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1631,18 +1987,18 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="S8" t="n">
         <v>11</v>
@@ -1651,64 +2007,78 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADO_J._SILVA</t>
+          <t>ADO_L._BOYLE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Silva</t>
+          <t>L. Boyle</t>
         </is>
       </c>
       <c r="C9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>11</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>9</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
         <v>7</v>
       </c>
-      <c r="D9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="R9" t="n">
         <v>10</v>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>7</v>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>8</v>
-      </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>3</v>
-      </c>
-      <c r="S9" t="n">
-        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -1723,59 +2093,69 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D10" t="n">
+        <v>6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>16</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>11</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>78.6%</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>11</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="n">
         <v>3</v>
       </c>
-      <c r="E10" t="n">
-        <v>9</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
-        <v>8</v>
-      </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>4</v>
-      </c>
-      <c r="S10" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1790,34 +2170,34 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1825,16 +2205,16 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -1849,10 +2229,10 @@
         <v>10</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12">
@@ -2011,7 +2391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2135,132 +2515,128 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADO_L._AYERS</t>
+          <t>ADO_R._SOEIRO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>L. Ayers</t>
+          <t>R. Soeiro</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>81.8%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Corner 3 Left</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="E2" t="n">
-        <v>32</v>
-      </c>
-      <c r="F2" t="n">
-        <v>16</v>
-      </c>
-      <c r="G2" t="n">
-        <v>39</v>
-      </c>
-      <c r="H2" t="n">
-        <v>14</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>43.8%</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L2" t="n">
-        <v>11</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>54.5%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O2" t="n">
-        <v>8</v>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>62.5%</t>
-        </is>
-      </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_J._PALM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>J. Palm</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H3" t="n">
-        <v>9</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2269,32 +2645,30 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADO_J._WOOD</t>
+          <t>ADO_N._MORAIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2302,29 +2676,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" t="n">
         <v>16</v>
       </c>
-      <c r="F4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G4" t="n">
-        <v>18</v>
-      </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2333,93 +2707,93 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>2</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>3</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADO_D._CAMBRIDGE</t>
+          <t>ADO_J._WOOD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D. Cambridge</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>21</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H5" t="n">
+        <v>13</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>61.9%</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
         <v>6</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>13</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>53.8%</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -2434,168 +2808,470 @@
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADO_L._BOYLE</t>
+          <t>ADO_L._AYERS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
+        <v>48</v>
+      </c>
+      <c r="H6" t="n">
+        <v>17</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>37.8%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>14</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
         <v>11</v>
       </c>
-      <c r="H6" t="n">
-        <v>9</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>6</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADO_M._MONTEIRO</t>
+          <t>ADO_D._CAMBRIDGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>D. Cambridge</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>16</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>6</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ADO_R._WOODS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>R. Woods</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" t="n">
+        <v>11</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>9</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>7</v>
+      </c>
+      <c r="R8" t="n">
+        <v>5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADO_J._SILVA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>J. Silva</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>17</v>
+      </c>
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>13</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ADO_M._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>M. Monteiro</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>32.0%</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" t="n">
+        <v>8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>8</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O10" t="n">
+        <v>7</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>9</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ADO_L._BOYLE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>L. Boyle</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>16</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>11</v>
+      </c>
+      <c r="H11" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>9</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>10</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S11" t="n">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S7"/>
+  <autoFilter ref="A1:S11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2709,41 +3385,41 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>37.8%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H2" t="n">
+        <v>48</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>14</v>
       </c>
-      <c r="D2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>43.8%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>32</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>54.5%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -2765,26 +3441,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I3" t="n">
         <v>1.1</v>
@@ -2795,11 +3471,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -2812,110 +3488,110 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_L._BOYLE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>L. Boyle</t>
         </is>
       </c>
       <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>16</v>
+      </c>
+      <c r="H4" t="n">
+        <v>11</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
         <v>9</v>
       </c>
-      <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>64.3%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>14</v>
-      </c>
-      <c r="H4" t="n">
-        <v>16</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>7</v>
-      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADO_L._BOYLE</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="C5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>20</v>
+      </c>
+      <c r="H5" t="n">
+        <v>20</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
         <v>9</v>
       </c>
-      <c r="D5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>12</v>
-      </c>
-      <c r="H5" t="n">
-        <v>11</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>6</v>
-      </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
@@ -2933,29 +3609,29 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -2963,71 +3639,71 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADO_M._MONTEIRO</t>
+          <t>ADO_D._CAMBRIDGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>D. Cambridge</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H7" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
         <v>6</v>
@@ -3036,113 +3712,113 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADO_R._SOEIRO</t>
+          <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R. Soeiro</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
         <v>6</v>
       </c>
-      <c r="D8" t="n">
-        <v>4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>6</v>
-      </c>
-      <c r="H8" t="n">
-        <v>12</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>3</v>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>66.7%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
       <c r="N8" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADO_D._CAMBRIDGE</t>
+          <t>ADO_R._SOEIRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D. Cambridge</t>
+          <t>R. Soeiro</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>81.8%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>11</v>
+      </c>
+      <c r="H9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>8</v>
+      </c>
+      <c r="N9" t="n">
         <v>2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>28.6%</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>21</v>
-      </c>
-      <c r="H9" t="n">
-        <v>22</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>13</v>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>53.8%</t>
-        </is>
-      </c>
-      <c r="M9" t="n">
-        <v>7</v>
-      </c>
-      <c r="N9" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -3260,12 +3936,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ADO_J._PALM</t>
+          <t>ADO_J._SILVA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>J. Palm</t>
+          <t>J. Silva</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3281,10 +3957,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I12" t="n">
         <v>0.9</v>
@@ -3295,11 +3971,11 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -3310,12 +3986,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ADO_J._SILVA</t>
+          <t>ADO_J._PALM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>J. Silva</t>
+          <t>J. Palm</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3331,13 +4007,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -3345,11 +4021,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -3369,11 +4045,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -3472,41 +4148,41 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>17</v>
+      </c>
+      <c r="D2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>37.8%</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>45</v>
+      </c>
+      <c r="H2" t="n">
+        <v>48</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>14</v>
       </c>
-      <c r="D2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>50.0%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>43.8%</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>32</v>
-      </c>
-      <c r="H2" t="n">
-        <v>39</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>11</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>54.5%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -3528,26 +4204,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H3" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I3" t="n">
         <v>1.1</v>
@@ -3558,11 +4234,11 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M3" t="n">
@@ -3572,8 +4248,288 @@
         <v>3</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ADO_R._WOODS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>R. Woods</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>9</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ADO_N._MORAIS</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>N. Morais</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>11</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>78.6%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" t="n">
+        <v>16</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>11</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ADO_D._CAMBRIDGE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>D. Cambridge</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" t="n">
+        <v>31</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>16</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>6</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ADO_L._BOYLE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>L. Boyle</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="n">
+        <v>11</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ADO_M._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>M. Monteiro</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>10</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>25</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>8</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>6</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N3"/>
+  <autoFilter ref="A1:N8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3652,32 +4608,32 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -3687,17 +4643,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3705,7 +4661,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -3722,77 +4678,77 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>4</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -3802,57 +4758,57 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>5</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -3987,24 +4943,24 @@
         </is>
       </c>
       <c r="D2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>11</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>54.5%</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4013,31 +4969,31 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="3">
@@ -4057,11 +5013,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -4070,11 +5026,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -4083,27 +5039,27 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -4113,12 +5069,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADO_J._WOOD</t>
+          <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4127,45 +5083,45 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="N4" t="n">
@@ -4173,22 +5129,22 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADO_M._MONTEIRO</t>
+          <t>ADO_J._WOOD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4197,16 +5153,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -4219,7 +5175,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -4227,27 +5183,27 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="6">
@@ -4267,11 +5223,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -4280,7 +5236,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -4293,99 +5249,95 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADO_L._BOYLE</t>
+          <t>ADO_J._SILVA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>J. Silva</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>9</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>0.9</v>
       </c>
@@ -4407,11 +5359,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -4420,22 +5372,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -4443,53 +5395,77 @@
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADO_J._SILVA</t>
+          <t>ADO_L._BOYLE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Silva</t>
+          <t>L. Boyle</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>71.4%</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="10">
@@ -4509,37 +5485,57 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>14</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>42.9%</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="n">
-        <v>7</v>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>42.9%</t>
-        </is>
-      </c>
       <c r="N10" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="11">
@@ -4559,16 +5555,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Corner 3 Right</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4581,35 +5577,35 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="12">
@@ -4734,7 +5730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4824,17 +5820,17 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -4842,7 +5838,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -4869,25 +5865,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="J3" t="n">
@@ -4900,12 +5896,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADO_L._AYERS</t>
+          <t>ADO_J._SILVA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>L. Ayers</t>
+          <t>J. Silva</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4914,29 +5910,29 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>76.5%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -4945,12 +5941,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADO_J._SILVA</t>
+          <t>ADO_J._PALM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Silva</t>
+          <t>J. Palm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4959,25 +5955,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -4990,43 +5986,43 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_L._AYERS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E6" t="n">
         <v>7</v>
       </c>
-      <c r="E6" t="n">
-        <v>4</v>
-      </c>
       <c r="F6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -5049,25 +6045,25 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -5080,57 +6076,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADO_J._PALM</t>
+          <t>ADO_L._AYERS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J. Palm</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADO_L._BOYLE</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -5139,25 +6135,25 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -5170,95 +6166,410 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ADO_L._AYERS</t>
+          <t>ADO_L._BOYLE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>L. Ayers</t>
+          <t>L. Boyle</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>9</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="n">
         <v>6</v>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>ADO_D._CAMBRIDGE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D. Cambridge</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>9</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>37.5%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>M. Monteiro</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D12" t="n">
+        <v>8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>32.0%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ADO_M._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>M. Monteiro</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>28.0%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ADO_L._AYERS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>L. Ayers</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>13.3%</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ADO_J._WOOD</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>J. Wood</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ADO_M._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>M. Monteiro</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>24.0%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ADO_J._PALM</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>J. Palm</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>5</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>31.2%</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ADO_R._SOEIRO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>R. Soeiro</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K11"/>
+  <autoFilter ref="A1:K18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_ADO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/shot_packs/shot_pack_ADO.xlsx
@@ -24,11 +24,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'players_volume'!$A$1:$S$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'players_eff'!$A$1:$S$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'players_3pt_volume'!$A$1:$N$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'players_3pt_pct'!$A$1:$N$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'team_zones'!$A$1:$I$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'preferred_areas'!$A$1:$P$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'player_zones_volume'!$A$1:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'player_zones_pct'!$A$1:$K$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,38 +590,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>219</v>
+        <v>278</v>
       </c>
       <c r="D2" t="n">
-        <v>93</v>
+        <v>118</v>
       </c>
       <c r="E2" t="n">
-        <v>220</v>
+        <v>276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -633,11 +633,11 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -646,15 +646,15 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T2" t="n">
         <v>8</v>
@@ -663,7 +663,7 @@
         <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="W2" t="n">
         <v>4</v>
@@ -681,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -771,17 +771,17 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -789,7 +789,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -816,17 +816,17 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -834,11 +834,11 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -861,25 +861,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -906,25 +906,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -937,12 +937,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADO_L._AYERS</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Ayers</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -969,25 +969,25 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_L._AYERS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -996,32 +996,32 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>19</v>
+      </c>
+      <c r="E7" t="n">
         <v>9</v>
       </c>
-      <c r="E7" t="n">
-        <v>4</v>
-      </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="J7" t="n">
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -1041,25 +1041,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -1131,17 +1131,17 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -1149,70 +1149,70 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ADO_L._BOYLE</t>
+          <t>ADO_L._AYERS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>8</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>27.4%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="F11" t="n">
-        <v>6</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>56.2%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ADO_L._AYERS</t>
+          <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L. Ayers</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1221,7 +1221,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="J12" t="n">
@@ -1249,8 +1249,53 @@
         <v>4</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ADO_L._BOYLE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>L. Boyle</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>57.9%</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K12"/>
+  <autoFilter ref="A1:K13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1288,7 +1333,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Maior volume: L. Ayers (45 L)</t>
+          <t>Maior volume: L. Ayers (62 L)</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1345,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Maior volume 3pt: L. Ayers (17 3PA)</t>
+          <t>Maior volume 3pt: L. Ayers (23 3PA)</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1357,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mais eficaz: R. Soeiro (1.3 pts/shot)</t>
+          <t>Mais eficaz: J. Palm (1.3 pts/shot)</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1369,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Zona mais usada: Above the Break 3 (71 L)</t>
+          <t>Zona mais usada: Above the Break 3 (85 L)</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1381,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zona mais eficaz: Restricted Area (54.4%)</t>
+          <t>Zona mais eficaz: Restricted Area (60.2%)</t>
         </is>
       </c>
     </row>
@@ -1485,30 +1530,30 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E2" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="J2" t="n">
@@ -1520,31 +1565,31 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -1562,69 +1607,69 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>38.2%</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>17</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>58.8%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
         <v>10</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>16</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>56.2%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>8</v>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1639,30 +1684,30 @@
         </is>
       </c>
       <c r="C4" t="n">
+        <v>34</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11</v>
+      </c>
+      <c r="E4" t="n">
         <v>25</v>
       </c>
-      <c r="D4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E4" t="n">
-        <v>18</v>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -1674,34 +1719,34 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R4" t="n">
         <v>9</v>
       </c>
       <c r="S4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1716,34 +1761,34 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -1764,18 +1809,18 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="S5" t="n">
         <v>2</v>
@@ -1793,34 +1838,34 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -1828,11 +1873,11 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1852,10 +1897,10 @@
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -1870,17 +1915,17 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1893,7 +1938,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1901,11 +1946,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1925,7 +1970,7 @@
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S7" t="n">
         <v>11</v>
@@ -1943,17 +1988,17 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1966,7 +2011,7 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1974,11 +2019,11 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1987,18 +2032,18 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>11</v>
@@ -2016,30 +2061,30 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="J9" t="n">
@@ -2051,11 +2096,11 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2064,11 +2109,11 @@
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -2093,7 +2138,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
@@ -2103,7 +2148,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2116,7 +2161,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -2137,7 +2182,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -2152,10 +2197,10 @@
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -2170,7 +2215,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
@@ -2180,59 +2225,59 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
         <v>9</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>81.8%</t>
-        </is>
-      </c>
-      <c r="J11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>5</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>2</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>10</v>
-      </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
@@ -2515,12 +2560,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADO_R._SOEIRO</t>
+          <t>ADO_J._PALM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>R. Soeiro</t>
+          <t>J. Palm</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2528,115 +2573,113 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G2" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H2" t="n">
-        <v>9</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>10</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADO_J._PALM</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Palm</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F3" t="n">
         <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2645,30 +2688,32 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q3" t="n">
         <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADO_N._MORAIS</t>
+          <t>ADO_L._AYERS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>N. Morais</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -2676,29 +2721,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2707,11 +2752,11 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2720,32 +2765,32 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="Q4" t="n">
         <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADO_J._WOOD</t>
+          <t>ADO_N._MORAIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2753,29 +2798,29 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2784,20 +2829,20 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Corner 3 Left</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -2808,7 +2853,7 @@
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -2817,12 +2862,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADO_L._AYERS</t>
+          <t>ADO_D._CAMBRIDGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Ayers</t>
+          <t>D. Cambridge</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2830,76 +2875,76 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="H6" t="n">
+        <v>13</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>30.8%</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>38.2%</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
         <v>17</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>47.1%</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>37.8%</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>58.8%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Above the Break 3</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>14</v>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
       <c r="O6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q6" t="n">
         <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADO_D._CAMBRIDGE</t>
+          <t>ADO_J._SILVA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Cambridge</t>
+          <t>J. Silva</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2907,76 +2952,70 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H7" t="n">
-        <v>10</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>17</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>58.8%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="O7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>33.3%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>16</v>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>56.2%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="O7" t="n">
-        <v>8</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>37.5%</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>6</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
         <v>6</v>
       </c>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_J._WOOD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2984,29 +3023,29 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3015,45 +3054,45 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>7</v>
       </c>
       <c r="R8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADO_J._SILVA</t>
+          <t>ADO_R._SOEIRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J. Silva</t>
+          <t>R. Soeiro</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3061,60 +3100,66 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
+        <v>12</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="Q9" t="n">
         <v>8</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3132,29 +3177,29 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="E10" t="n">
+        <v>34</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11</v>
+      </c>
+      <c r="G10" t="n">
         <v>25</v>
       </c>
-      <c r="F10" t="n">
-        <v>8</v>
-      </c>
-      <c r="G10" t="n">
-        <v>18</v>
-      </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3163,34 +3208,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="Q10" t="n">
         <v>9</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -3209,55 +3254,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>13</v>
+      </c>
+      <c r="H11" t="n">
+        <v>14</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>73.7%</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>11</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="O11" t="n">
         <v>4</v>
       </c>
-      <c r="G11" t="n">
-        <v>11</v>
-      </c>
-      <c r="H11" t="n">
-        <v>12</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>75.0%</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>9</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>22.2%</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>3</v>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -3267,7 +3312,7 @@
         <v>7</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3385,26 +3430,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="H2" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="I2" t="n">
         <v>1.1</v>
@@ -3415,11 +3460,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -3441,29 +3486,29 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="H3" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -3482,7 +3527,7 @@
         <v>2</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -3497,26 +3542,26 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I4" t="n">
         <v>0.7</v>
@@ -3527,111 +3572,111 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="M4" t="n">
         <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_D._CAMBRIDGE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>D. Cambridge</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="H5" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="M5" t="n">
         <v>4</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADO_N._MORAIS</t>
+          <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>N. Morais</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H6" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -3643,107 +3688,107 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="M6" t="n">
         <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADO_D._CAMBRIDGE</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D. Cambridge</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>52.2%</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>23</v>
+      </c>
+      <c r="H7" t="n">
+        <v>25</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
         <v>10</v>
       </c>
-      <c r="D7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>30.0%</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" t="n">
-        <v>31</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>16</v>
-      </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="M7" t="n">
         <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADO_M._MONTEIRO</t>
+          <t>ADO_R._SOEIRO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>R. Soeiro</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H8" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -3751,74 +3796,74 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M8" t="n">
         <v>6</v>
       </c>
       <c r="N8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADO_R._SOEIRO</t>
+          <t>ADO_N._MORAIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R. Soeiro</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="n">
+        <v>16</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
         <v>11</v>
       </c>
-      <c r="H9" t="n">
-        <v>14</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Above the Break 3</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>5</v>
-      </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="M9" t="n">
         <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -3957,25 +4002,25 @@
         </is>
       </c>
       <c r="G12" t="n">
+        <v>21</v>
+      </c>
+      <c r="H12" t="n">
+        <v>22</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
         <v>17</v>
       </c>
-      <c r="H12" t="n">
-        <v>16</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Restricted Area</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>13</v>
-      </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="M12" t="n">
@@ -4007,13 +4052,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H13" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -4021,11 +4066,11 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="M13" t="n">
@@ -4045,7 +4090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4148,26 +4193,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="H2" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="I2" t="n">
         <v>1.1</v>
@@ -4178,11 +4223,11 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="M2" t="n">
@@ -4195,35 +4240,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADO_J._WOOD</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I3" t="n">
         <v>1.1</v>
@@ -4234,29 +4279,29 @@
         </is>
       </c>
       <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
         <v>6</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_N._MORAIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -4272,17 +4317,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -4290,55 +4335,55 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="N4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADO_N._MORAIS</t>
+          <t>ADO_R._SOEIRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N. Morais</t>
+          <t>R. Soeiro</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" t="n">
         <v>14</v>
       </c>
-      <c r="H5" t="n">
-        <v>16</v>
-      </c>
       <c r="I5" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -4346,15 +4391,15 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N5" t="n">
         <v>4</v>
@@ -4372,29 +4417,29 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H6" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -4402,55 +4447,55 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADO_L._BOYLE</t>
+          <t>ADO_J._WOOD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="H7" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -4458,18 +4503,18 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -4484,26 +4529,26 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>34</v>
+      </c>
+      <c r="H8" t="n">
         <v>25</v>
-      </c>
-      <c r="H8" t="n">
-        <v>18</v>
       </c>
       <c r="I8" t="n">
         <v>0.7</v>
@@ -4514,22 +4559,78 @@
         </is>
       </c>
       <c r="K8" t="n">
+        <v>11</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>4</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ADO_L._BOYLE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>L. Boyle</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>21.4%</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>73.7%</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>19</v>
+      </c>
+      <c r="H9" t="n">
+        <v>13</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>11</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>18.2%</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>3</v>
+      </c>
+      <c r="N9" t="n">
         <v>8</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="M8" t="n">
-        <v>6</v>
-      </c>
-      <c r="N8" t="n">
-        <v>8</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N8"/>
+  <autoFilter ref="A1:N9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4608,17 +4709,17 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -4626,14 +4727,14 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="H2" t="n">
         <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -4643,25 +4744,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="D3" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -4678,17 +4779,17 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C4" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -4696,14 +4797,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -4713,25 +4814,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -4748,7 +4849,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
@@ -4758,15 +4859,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -4783,32 +4884,32 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>6</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4943,53 +5044,53 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>17</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>23.5%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>11</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>63.6%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
       <c r="J2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -5013,11 +5114,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5026,11 +5127,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -5047,23 +5148,23 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -5083,53 +5184,53 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>22.2%</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Restricted Area</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>7</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>42.9%</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Paint Non-RA</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>6</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
       <c r="L4" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -5166,11 +5267,11 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -5179,31 +5280,31 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -5223,11 +5324,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5249,31 +5350,31 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="7">
@@ -5293,11 +5394,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -5327,11 +5428,11 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="N7" t="n">
@@ -5339,7 +5440,7 @@
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -5359,11 +5460,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5372,22 +5473,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="N8" t="n">
@@ -5395,7 +5496,7 @@
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="9">
@@ -5415,11 +5516,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -5428,11 +5529,11 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -5449,19 +5550,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -5494,7 +5595,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Mid-Range</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -5507,23 +5608,23 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Mid-Range</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="N10" t="n">
@@ -5555,29 +5656,29 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>Corner 3 Left</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>2</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Corner 3 Right</t>
         </is>
       </c>
       <c r="J11" t="n">
@@ -5589,23 +5690,23 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12">
@@ -5730,7 +5831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5806,91 +5907,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ADO_D._CAMBRIDGE</t>
+          <t>ADO_L._AYERS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D. Cambridge</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
         <v>9</v>
       </c>
       <c r="F2" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADO_L._AYERS</t>
+          <t>ADO_D._CAMBRIDGE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>L. Ayers</t>
+          <t>D. Cambridge</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>58.8%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>50.0%</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>31.1%</t>
-        </is>
-      </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -5910,25 +6011,25 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -5941,46 +6042,46 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ADO_J._PALM</t>
+          <t>ADO_L._AYERS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>J. Palm</t>
+          <t>L. Ayers</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" t="n">
         <v>8</v>
       </c>
-      <c r="F5" t="n">
-        <v>16</v>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -6000,17 +6101,17 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -6018,11 +6119,11 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -6031,39 +6132,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ADO_N._MORAIS</t>
+          <t>ADO_J._PALM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>N. Morais</t>
+          <t>J. Palm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J7" t="n">
@@ -6076,57 +6177,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ADO_L._AYERS</t>
+          <t>ADO_N._MORAIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>L. Ayers</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ADO_R._WOODS</t>
+          <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6135,32 +6236,32 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>11</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
         <v>9</v>
       </c>
-      <c r="E9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" t="n">
-        <v>12</v>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -6180,7 +6281,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
@@ -6190,15 +6291,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="J10" t="n">
@@ -6211,12 +6312,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ADO_D._CAMBRIDGE</t>
+          <t>ADO_R._WOODS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D. Cambridge</t>
+          <t>R. Woods</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -6225,43 +6326,43 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ADO_M._MONTEIRO</t>
+          <t>ADO_D._CAMBRIDGE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>D. Cambridge</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6270,29 +6371,29 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>29.4%</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
         <v>2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>6</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>32.0%</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -6311,36 +6412,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Restricted Area</t>
+          <t>Paint Non-RA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="J13" t="n">
         <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14">
@@ -6360,7 +6461,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
@@ -6370,78 +6471,78 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="J14" t="n">
         <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ADO_J._WOOD</t>
+          <t>ADO_M._MONTEIRO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Restricted Area</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
         <v>6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ADO_M._MONTEIRO</t>
+          <t>ADO_J._PALM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>M. Monteiro</t>
+          <t>J. Palm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6453,94 +6554,94 @@
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>31.6%</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>24.0%</t>
-        </is>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
-      </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ADO_J._PALM</t>
+          <t>ADO_J._WOOD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>J. Palm</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Paint Non-RA</t>
+          <t>Above the Break 3</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E17" t="n">
         <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ADO_R._SOEIRO</t>
+          <t>ADO_J._WOOD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R. Soeiro</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Above the Break 3</t>
+          <t>Corner 3 Left</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
         <v>2</v>
@@ -6550,26 +6651,251 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ADO_R._SOEIRO</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>R. Soeiro</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Above the Break 3</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>40.0%</t>
         </is>
       </c>
-      <c r="H18" t="n">
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ADO_J._WOOD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>J. Wood</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Corner 3 Right</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>18.8%</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ADO_J._WOOD</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>J. Wood</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Paint Non-RA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>80.0%</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ADO_J._WOOD</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>J. Wood</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Restricted Area</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
         <v>1.2</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>15.6%</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ADO_M._MONTEIRO</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>M. Monteiro</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Mid-Range</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>14.7%</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K18"/>
+  <autoFilter ref="A1:K23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>